--- a/WorkBot/refactor/data/orders/Performance Food/CompletedOrders/Performance Food_Collegetown_2025-10-08.xlsx
+++ b/WorkBot/refactor/data/orders/Performance Food/CompletedOrders/Performance Food_Collegetown_2025-10-08.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -848,6 +848,411 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>23978</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Monin - Vanilla</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>35.21</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>140.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>44256</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PKT Sugar - (Raw)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>34.14</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>34.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>T0948</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Almond Milk</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>35.74</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>321.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CR202</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pretzel - Soft Jumbo</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>46.96</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>46.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MN198</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tuna - Ahi (Sesame Seared)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>174.60</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>174.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A0280</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Edamame - FRZ Shelled</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>48.00</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>48.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DV584</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sweet Encore - Key Lime Pie</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>62.50</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>62.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>FB268</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Mousse Cup - Chocolate</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>31.25</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>62.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FV234</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Poland Spring - Sport Top</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>11.09</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>88.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AT104</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Simply - Orange</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>44.33</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>44.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AKJ04</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Joe Tea - Black Unsweetened</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>21.95</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>21.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ED258</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Spindrift - Lemon</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>24.83</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>24.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CR620</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Spindrift - Orange Mango</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>24.96</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>24.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>99482</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sparkling Ice - Orange Mango</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>12.32</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>12.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>B2368</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sparkling Ice - Cherry Limeade</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>12.32</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>12.32</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
